--- a/raspberry-pi/enclosure/xlsx/hardware.xlsx
+++ b/raspberry-pi/enclosure/xlsx/hardware.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,7 +158,14 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -901,7 +908,7 @@
           <t>&lt; 0.1 Ω</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
@@ -918,7 +925,7 @@
           <t>도통</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
       <c r="E6" s="10" t="inlineStr">
         <is>
           <t>★ 빠지면 현장에서 간헐적 CRC 오류</t>
@@ -939,7 +946,7 @@
           <t>도통</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr"/>
       <c r="E7" s="10" t="inlineStr">
         <is>
           <t>★ 위와 한 쌍</t>
@@ -960,7 +967,7 @@
           <t>≥ 10 MΩ</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
@@ -977,7 +984,7 @@
           <t>11.5 ~ 12.5 V</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
+      <c r="D9" s="22" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -994,7 +1001,7 @@
           <t>220 V ± 10%</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr"/>
+      <c r="D10" s="22" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1011,7 +1018,7 @@
           <t>12 V ± 0.5</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr"/>
+      <c r="D11" s="22" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1028,7 +1035,7 @@
           <t>3포트 동일값</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr"/>
+      <c r="D12" s="22" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>병렬 결선 확인</t>
@@ -1049,7 +1056,7 @@
           <t>약 16 W ± 20%</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr"/>
+      <c r="D13" s="22" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1066,7 +1073,7 @@
           <t>계기판 정상 표시</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr"/>
+      <c r="D14" s="22" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1083,7 +1090,7 @@
           <t>네 모서리 + 중앙 5점</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr"/>
+      <c r="D15" s="22" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1100,7 +1107,7 @@
           <t>연결한 ID 가 모두 응답</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr"/>
+      <c r="D16" s="22" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1117,7 +1124,7 @@
           <t>4개 값 출력</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr"/>
+      <c r="D17" s="22" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1134,7 +1141,7 @@
           <t>6자리 코드 표시</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr"/>
+      <c r="D18" s="22" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1151,7 +1158,7 @@
           <t>시각 유지</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="D19" s="22" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1168,7 +1175,7 @@
           <t>CPU &lt; 75℃, 스로틀 로그 없음</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr"/>
+      <c r="D20" s="22" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1185,7 +1192,7 @@
           <t>이상 없음</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr"/>
+      <c r="D21" s="22" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1202,7 +1209,7 @@
           <t>RS485 배선 이상 없음</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr"/>
+      <c r="D22" s="22" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>도어 가동부 통과선</t>
@@ -1223,7 +1230,7 @@
           <t>이상 없음</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="D23" s="22" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1460,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2793,8 +2800,8 @@
         </is>
       </c>
       <c r="E45" s="11">
-        <f>COUNTIF(F7:F43,"확인완료")</f>
-        <v/>
+        <f>COUNTIF(F5:F43,"확인완료")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2804,8 +2811,19 @@
         </is>
       </c>
       <c r="E46" s="11">
-        <f>COUNTIF(F7:F43,"확인필요")</f>
-        <v/>
+        <f>COUNTIF(F5:F43,"확인필요")</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>제작 품목 수</t>
+        </is>
+      </c>
+      <c r="E47" s="11">
+        <f>COUNTIF(F5:F43,"제작")</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4330,13 +4348,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4349,7 +4368,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>파란 글씨 = 입력값 / 검정 = 수식. 값을 바꾸면 아래 열 계산이 따라옵니다.</t>
+          <t>파란 글씨 = 입력값 / 검정 = 수식.  내부발열 Y = 함체 안에서 열이 되는 것, N = 밖으로 나가는 것</t>
         </is>
       </c>
     </row>
@@ -4371,6 +4390,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>내부발열</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>근거</t>
         </is>
       </c>
@@ -4389,7 +4413,12 @@
           <t>W</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>피크 기준</t>
         </is>
@@ -4409,7 +4438,12 @@
           <t>W</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>백라이트 최대 포함</t>
         </is>
@@ -4429,7 +4463,12 @@
           <t>W</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>효율 0.85, 출력 10W 기준</t>
         </is>
@@ -4449,118 +4488,141 @@
           <t>W</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>센서 3대 @ 12V</t>
+          <t>SMPS 손실 (경부하)</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>대당 약 30mA</t>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>부하율 2% 라 무부하 손실이 지배</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>SMPS 손실 (경부하)</t>
+          <t>센서 3대 @ 12V</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>부하율 2% 라 무부하 손실이 지배</t>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>케이블로 함체 밖 센서에서 소비 — 내부 발열 아님</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>함체 내부 발열 합계</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>AC 총 소비</t>
+        </is>
+      </c>
+      <c r="B11" s="17">
         <f>SUM(B5:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
+        <v>14.6</v>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>정격 라벨용</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>함체 내부 발열</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>SUMIF(D5:D10,"Y",B5:B10)</f>
+        <v>13.4</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>열 설계의 입력값</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>열 설계 — 하이박스 300 × 300 × 165</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>외형 W</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>300</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>확정</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>외형 H</t>
+          <t>외형 W</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
@@ -4571,7 +4633,8 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
@@ -4580,18 +4643,19 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>외형 D</t>
+          <t>외형 H</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>확정</t>
         </is>
@@ -4600,109 +4664,135 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>열전달계수 k</t>
+          <t>외형 D</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>3.5</v>
+        <v>165</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>W/㎡·K</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>플라스틱 자연대류</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>전체 표면적</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>2*(B16*B17+B16*B18+B17*B18)/1000000</f>
-        <v/>
+          <t>열전달계수 k</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>3.5</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>㎡</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>6면 합</t>
+          <t>W/㎡·K</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>플라스틱 자연대류</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>유효 표면적</t>
+          <t>전체 표면적</t>
         </is>
       </c>
       <c r="B21" s="8">
-        <f>B20-(B16*B17)/1000000</f>
-        <v/>
+        <f>2*(B17*B18+B17*B19+B18*B19)/1000000</f>
+        <v>0.378</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
           <t>㎡</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>벽부 설치 — 후면 제외</t>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>6면 합</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>유효 표면적</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>B21-(B17*B18)/1000000</f>
+        <v>0.288</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>벽부 설치 — 후면 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>내부 온도 상승 ΔT</t>
         </is>
       </c>
-      <c r="B22" s="8">
-        <f>B11/(B19*B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B23" s="8">
+        <f>B12/(B20*B22)</f>
+        <v>13.29</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>발열 / (k × 유효면적)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>내부 발열 / (k × 유효면적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>여름 그늘 40℃ 에서 내부</t>
         </is>
       </c>
-      <c r="B23" s="15">
-        <f>40+B22</f>
-        <v/>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B24" s="17">
+        <f>40+B23</f>
+        <v>53.29</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>허용 (CPU 약 70℃, 스로틀 80℃)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>직사광에 노출되면 내부가 70℃ 를 넘습니다. 그늘에 설치하거나 차양(SH-05)을 다십시오. 환기 팬·통풍구는 달지 마십시오 — 염분과 습기를 빨아들여 방열로 얻는 것보다 부식으로 잃는 것이 큽니다.</t>
         </is>
@@ -4827,31 +4917,31 @@
       </c>
       <c r="E5" s="8">
         <f>B5-$B$17</f>
-        <v/>
+        <v>85</v>
       </c>
       <c r="F5" s="8">
         <f>C5-$B$17</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="G5" s="8">
         <f>D5-$B$18</f>
-        <v/>
+        <v>57</v>
       </c>
       <c r="H5" s="8">
         <f>E5-$B$19</f>
-        <v/>
+        <v>-165</v>
       </c>
       <c r="I5" s="8">
         <f>F5-$B$20</f>
-        <v/>
+        <v>-85</v>
       </c>
       <c r="J5" s="8">
         <f>G5-$B$21</f>
-        <v/>
-      </c>
-      <c r="K5" s="8">
+        <v>-63</v>
+      </c>
+      <c r="K5" s="8" t="str">
         <f>IF(AND(H5&gt;=0,I5&gt;=0,J5&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>불가</v>
       </c>
       <c r="L5" s="8" t="inlineStr"/>
     </row>
@@ -4870,31 +4960,31 @@
       </c>
       <c r="E6" s="8">
         <f>B6-$B$17</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="F6" s="8">
         <f>C6-$B$17</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="G6" s="8">
         <f>D6-$B$18</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="H6" s="8">
         <f>E6-$B$19</f>
-        <v/>
+        <v>-115</v>
       </c>
       <c r="I6" s="8">
         <f>F6-$B$20</f>
-        <v/>
+        <v>-85</v>
       </c>
       <c r="J6" s="8">
         <f>G6-$B$21</f>
-        <v/>
-      </c>
-      <c r="K6" s="8">
+        <v>-53</v>
+      </c>
+      <c r="K6" s="8" t="str">
         <f>IF(AND(H6&gt;=0,I6&gt;=0,J6&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>불가</v>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
     </row>
@@ -4913,31 +5003,31 @@
       </c>
       <c r="E7" s="8">
         <f>B7-$B$17</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="F7" s="8">
         <f>C7-$B$17</f>
-        <v/>
+        <v>185</v>
       </c>
       <c r="G7" s="8">
         <f>D7-$B$18</f>
-        <v/>
+        <v>107</v>
       </c>
       <c r="H7" s="8">
         <f>E7-$B$19</f>
-        <v/>
+        <v>-115</v>
       </c>
       <c r="I7" s="8">
         <f>F7-$B$20</f>
-        <v/>
+        <v>-35</v>
       </c>
       <c r="J7" s="8">
         <f>G7-$B$21</f>
-        <v/>
-      </c>
-      <c r="K7" s="8">
+        <v>-13</v>
+      </c>
+      <c r="K7" s="8" t="str">
         <f>IF(AND(H7&gt;=0,I7&gt;=0,J7&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>불가</v>
       </c>
       <c r="L7" s="8" t="inlineStr"/>
     </row>
@@ -4956,31 +5046,31 @@
       </c>
       <c r="E8" s="8">
         <f>B8-$B$17</f>
-        <v/>
+        <v>185</v>
       </c>
       <c r="F8" s="8">
         <f>C8-$B$17</f>
-        <v/>
+        <v>285</v>
       </c>
       <c r="G8" s="8">
         <f>D8-$B$18</f>
-        <v/>
+        <v>107</v>
       </c>
       <c r="H8" s="8">
         <f>E8-$B$19</f>
-        <v/>
+        <v>-65</v>
       </c>
       <c r="I8" s="8">
         <f>F8-$B$20</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="J8" s="8">
         <f>G8-$B$21</f>
-        <v/>
-      </c>
-      <c r="K8" s="8">
+        <v>-13</v>
+      </c>
+      <c r="K8" s="8" t="str">
         <f>IF(AND(H8&gt;=0,I8&gt;=0,J8&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>불가</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -4989,47 +5079,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="20" t="n">
         <v>300</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="20" t="n">
         <v>300</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="20" t="n">
         <v>165</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="19">
         <f>B9-$B$17</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
+        <v>285</v>
+      </c>
+      <c r="F9" s="19">
         <f>C9-$B$17</f>
-        <v/>
-      </c>
-      <c r="G9" s="16">
+        <v>285</v>
+      </c>
+      <c r="G9" s="19">
         <f>D9-$B$18</f>
-        <v/>
-      </c>
-      <c r="H9" s="16">
+        <v>142</v>
+      </c>
+      <c r="H9" s="19">
         <f>E9-$B$19</f>
-        <v/>
-      </c>
-      <c r="I9" s="16">
+        <v>35</v>
+      </c>
+      <c r="I9" s="19">
         <f>F9-$B$20</f>
-        <v/>
-      </c>
-      <c r="J9" s="16">
+        <v>65</v>
+      </c>
+      <c r="J9" s="19">
         <f>G9-$B$21</f>
-        <v/>
-      </c>
-      <c r="K9" s="16">
+        <v>22</v>
+      </c>
+      <c r="K9" s="19" t="str">
         <f>IF(AND(H9&gt;=0,I9&gt;=0,J9&gt;=0),"가능","불가")</f>
-        <v/>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+        <v>가능</v>
+      </c>
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t>★ 선정 — 깊이 여유 최대, 정사각이라 표기 혼동 없음</t>
         </is>
@@ -5050,31 +5140,31 @@
       </c>
       <c r="E10" s="8">
         <f>B10-$B$17</f>
-        <v/>
+        <v>285</v>
       </c>
       <c r="F10" s="8">
         <f>C10-$B$17</f>
-        <v/>
+        <v>385</v>
       </c>
       <c r="G10" s="8">
         <f>D10-$B$18</f>
-        <v/>
+        <v>127</v>
       </c>
       <c r="H10" s="8">
         <f>E10-$B$19</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="I10" s="8">
         <f>F10-$B$20</f>
-        <v/>
+        <v>165</v>
       </c>
       <c r="J10" s="8">
         <f>G10-$B$21</f>
-        <v/>
-      </c>
-      <c r="K10" s="8">
+        <v>7</v>
+      </c>
+      <c r="K10" s="8" t="str">
         <f>IF(AND(H10&gt;=0,I10&gt;=0,J10&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>가능</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -5097,31 +5187,31 @@
       </c>
       <c r="E11" s="8">
         <f>B11-$B$17</f>
-        <v/>
+        <v>385</v>
       </c>
       <c r="F11" s="8">
         <f>C11-$B$17</f>
-        <v/>
+        <v>485</v>
       </c>
       <c r="G11" s="8">
         <f>D11-$B$18</f>
-        <v/>
+        <v>137</v>
       </c>
       <c r="H11" s="8">
         <f>E11-$B$19</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="I11" s="8">
         <f>F11-$B$20</f>
-        <v/>
+        <v>265</v>
       </c>
       <c r="J11" s="8">
         <f>G11-$B$21</f>
-        <v/>
-      </c>
-      <c r="K11" s="8">
+        <v>17</v>
+      </c>
+      <c r="K11" s="8" t="str">
         <f>IF(AND(H11&gt;=0,I11&gt;=0,J11&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>가능</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -5144,31 +5234,31 @@
       </c>
       <c r="E12" s="8">
         <f>B12-$B$17</f>
-        <v/>
+        <v>485</v>
       </c>
       <c r="F12" s="8">
         <f>C12-$B$17</f>
-        <v/>
+        <v>585</v>
       </c>
       <c r="G12" s="8">
         <f>D12-$B$18</f>
-        <v/>
+        <v>167</v>
       </c>
       <c r="H12" s="8">
         <f>E12-$B$19</f>
-        <v/>
+        <v>235</v>
       </c>
       <c r="I12" s="8">
         <f>F12-$B$20</f>
-        <v/>
+        <v>365</v>
       </c>
       <c r="J12" s="8">
         <f>G12-$B$21</f>
-        <v/>
-      </c>
-      <c r="K12" s="8">
+        <v>47</v>
+      </c>
+      <c r="K12" s="8" t="str">
         <f>IF(AND(H12&gt;=0,I12&gt;=0,J12&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>가능</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -5191,31 +5281,31 @@
       </c>
       <c r="E13" s="8">
         <f>B13-$B$17</f>
-        <v/>
+        <v>585</v>
       </c>
       <c r="F13" s="8">
         <f>C13-$B$17</f>
-        <v/>
+        <v>685</v>
       </c>
       <c r="G13" s="8">
         <f>D13-$B$18</f>
-        <v/>
+        <v>177</v>
       </c>
       <c r="H13" s="8">
         <f>E13-$B$19</f>
-        <v/>
+        <v>335</v>
       </c>
       <c r="I13" s="8">
         <f>F13-$B$20</f>
-        <v/>
+        <v>465</v>
       </c>
       <c r="J13" s="8">
         <f>G13-$B$21</f>
-        <v/>
-      </c>
-      <c r="K13" s="8">
+        <v>57</v>
+      </c>
+      <c r="K13" s="8" t="str">
         <f>IF(AND(H13&gt;=0,I13&gt;=0,J13&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>가능</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -5238,31 +5328,31 @@
       </c>
       <c r="E14" s="8">
         <f>B14-$B$17</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="F14" s="8">
         <f>C14-$B$17</f>
-        <v/>
+        <v>120</v>
       </c>
       <c r="G14" s="8">
         <f>D14-$B$18</f>
-        <v/>
+        <v>62</v>
       </c>
       <c r="H14" s="8">
         <f>E14-$B$19</f>
-        <v/>
+        <v>-175</v>
       </c>
       <c r="I14" s="8">
         <f>F14-$B$20</f>
-        <v/>
+        <v>-100</v>
       </c>
       <c r="J14" s="8">
         <f>G14-$B$21</f>
-        <v/>
-      </c>
-      <c r="K14" s="8">
+        <v>-58</v>
+      </c>
+      <c r="K14" s="8" t="str">
         <f>IF(AND(H14&gt;=0,I14&gt;=0,J14&gt;=0),"가능","불가")</f>
-        <v/>
+        <v>불가</v>
       </c>
       <c r="L14" s="8" t="inlineStr"/>
     </row>
@@ -5279,7 +5369,7 @@
           <t>W·H 벽두께+실링립 손실</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="21" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -5294,7 +5384,7 @@
           <t>D 후면벽+도어립 손실</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="21" t="n">
         <v>23</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -5309,7 +5399,7 @@
           <t>요구 내부 W</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="21" t="n">
         <v>250</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -5324,7 +5414,7 @@
           <t>요구 내부 H</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="21" t="n">
         <v>220</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5339,7 +5429,7 @@
           <t>요구 내부 D</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="21" t="n">
         <v>120</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -6349,7 +6439,7 @@
           <t>센서 3대 전류</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="21" t="n">
         <v>0.09</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6369,7 +6459,7 @@
           <t>케이블 단면적</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="21" t="n">
         <v>0.5</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -6379,27 +6469,27 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>입력값</t>
+          <t>입력값 — 바꾸면 아래가 다시 계산됩니다</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>구리 저항률</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="n">
-        <v>0.0357</v>
+          <t>구리 고유저항</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>0.0178</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Ω/m·㎟</t>
+          <t>Ω·㎟/m</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>0.5㎟ 기준 0.0357 Ω/m</t>
+          <t>20℃ 연동 기준</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6499,7 @@
           <t>편도 길이</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="21" t="n">
         <v>50</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -6419,7 +6509,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>입력값</t>
+          <t>입력값 — 바꾸면 아래가 다시 계산됩니다</t>
         </is>
       </c>
     </row>
@@ -6430,8 +6520,8 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <f>B20*B21*2</f>
-        <v/>
+        <f>B20*B21*2/B19</f>
+        <v>3.56</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -6440,7 +6530,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>저항률 × 편도 × 2</t>
+          <t>고유저항 × 편도 × 2 ÷ 단면적</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6542,7 @@
       </c>
       <c r="B23" s="8">
         <f>B18*B22</f>
-        <v/>
+        <v>0.3204</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -6473,7 +6563,7 @@
       </c>
       <c r="B24" s="8">
         <f>12-B23</f>
-        <v/>
+        <v>11.6796</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -6487,14 +6577,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>하한 9V 대비 여유</t>
         </is>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="17">
         <f>B24-9</f>
-        <v/>
+        <v>2.6796</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>

--- a/raspberry-pi/enclosure/xlsx/hardware.xlsx
+++ b/raspberry-pi/enclosure/xlsx/hardware.xlsx
@@ -18,6 +18,7 @@
     <sheet name="9.전선규격" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="10.검사표" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="11.확인필요" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12.주문대조" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -132,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +173,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1461,6 +1463,1110 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>주문 목록 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 주문분과 BOM 을 맞춰 본 것입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>주문 품목</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>BOM 대응</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>확인할 것 / 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>직결나사 접시머리 직결피스 10종 500g</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>(고정용 나사)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>알루미늄 백플레이트 2t 에는 직결나사가 잘 안 물립니다. 하이박스 기본 내부판이 플라스틱이면 사용 가능. 금속판이면 M4 볼트+너트나 탭 가공 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>고정식 단자대 30A 8P 터미널블럭 × 5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2,990</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>33. 단자대 8P</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>정격 30A 로 충분. 극 사이 절연 격벽이 있는지 확인 — 220V 와 저압이 한 단자대에 섞입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>수축 튜브 세트 530p</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>3,590</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>(부속)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>압착부 절연·표시용</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>원스탑 만능 터미널압착기</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>(공구)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>절연 압착단자용 다이가 있는지 확인. 극당 3가닥을 압착단자로 정리해야 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>어반카 와이오 압착 단자 터미널 320p 세트</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>(부속)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>단자대 나사 규격(M3.5 또는 M4)에 맞는 링/Y 단자가 세트에 있는지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>몬스툴 전기 인두기 + 받침대 + 땜납</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>9,710</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>(공구)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>TVS 소자와 변환기 단자에 필요. 대부분은 나사 단자라 사용처는 적습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>5색 DIY 전선 30/26/22/20/18/16AWG UL1007 (옵션 30AWG/50M)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>14,900</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>38. 배선재</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>★ 확인 필요</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>선택 옵션이 30AWG(0.05㎟) 라면 이 장비에 쓸 수 있는 굵기가 하나도 없습니다. 아래 표 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>주문 합계</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>55990</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AWG ↔ ㎟ 대조 — 이 장비에 필요한 굵기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>AWG</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>단면적 ㎟</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>쓰는 곳</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>필요 여부</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>PE 주간선 (사양 1.5㎟ 에 근접)</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr"/>
+      <c r="F18" s="19" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>AC L·N / +12V / 0V / 본딩</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr"/>
+      <c r="F19" s="19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>RS485 A·B</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr"/>
+      <c r="F20" s="19" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>불필요</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>불필요</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>쓸 수 없음</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr"/>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>전류·강도 모두 부족</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>★ 필요한 것은 AWG 16 · 18 · 20 세 가지입니다. 주문 옵션이 30AWG 단품이면 16/18/20AWG 를 다시 주문하셔야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>UL1007 은 PVC 300V 정격, 실리콘 와이어는 보통 UL3132/3239 로 내열 200℃ 입니다. 상품명에 둘이 섞여 있으니 실제 어느 쪽인지 확인하십시오. AC 220V 배선에는 300V 이상 정격이 필요하고, SMPS 근처라면 실리콘 쪽이 내열에 유리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>RS485 는 함체 안 짧은 구간(변환기→TVS→단자대)이라 낱개 선으로도 되지만 A/B 를 꼬아 주십시오. 센서로 나가는 케이블은 반드시 실드 트위스트 페어여야 하며, 그것은 센서 케이블로 따로 준비합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>아직 주문되지 않은 품목</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>SMPS 12V 60W (5A)</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>지정 제품 — 외형·나사 피치 확인</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>콘센트 1구 원형 220V</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>지정 제품</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>파이 전원 어댑터 5.1V 3A</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>공식 어댑터</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>함체</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>하이박스 300×300×165</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>커버 체결 방식 확인 필수</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>함체</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>알루미늄 백플레이트</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>금속. 방열 경로</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>제어</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>라즈베리파이 4 + 7" 디스플레이</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>제어</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>USB-RS485 변환기 / SSD / RTC</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>커넥터</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>AC 인입 커넥터 + 케이블 플러그</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>센서용과 결합 불가한 형식</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>커넥터</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>M12 A-coded 센서 커넥터</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>3 + 예비 1</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>커넥터</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>M12 현장조립 플러그</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>커넥터</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>고어 통기 벤트 M12×1.5</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>결로 방지 — 빠뜨리기 쉬움</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>커넥터</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>방수캡</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>보호</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>퓨즈홀더 + 퓨즈 (AC 2A / 12V 1A)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr"/>
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>보호</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>SPD 275V (온도퓨즈 내장형)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>맨 바리스터 금지</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr"/>
+      <c r="F48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>보호</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>TVS — SM712 / 16V급</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr"/>
+      <c r="E49" s="9" t="inlineStr"/>
+      <c r="F49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>압착 프레임 (SH-04)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>알루미늄 3t 레이저 절단</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr"/>
+      <c r="F50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>개스킷 테이프 폭5×두께2 / 실리콘 패드 3t</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>M3 스탠드오프 Ø8 접착식</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>길이는 시제품 실측 후</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr"/>
+      <c r="F52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>SUS316 M4 핀-인-톡스 볼트 + 전용 비트</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>6 / 1</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>탬퍼 방지</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>봉인 라벨 VOID</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>접지 스터드 M4 + 톱니와셔</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>실리카겔 50g / 열전도 패드</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>각 1</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>종단저항 120Ω</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>케이블 10m 초과 시</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>케이블 타이 앵커 (접착식)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>1식</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>RS485용 실드 트위스트 페어 센서 케이블</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>현장별</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>0.5㎟ 이상. 50m 초과면 0.75㎟</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr"/>
+      <c r="F59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>라벨</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>정격·경고·커넥터·시리얼 라벨</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>1식</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>전면: 환경 모니터링 시스템 / 주식회사 컬리버</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/raspberry-pi/enclosure/xlsx/hardware.xlsx
+++ b/raspberry-pi/enclosure/xlsx/hardware.xlsx
@@ -18,7 +18,7 @@
     <sheet name="9.전선규격" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="10.검사표" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="11.확인필요" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12.주문대조" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12.구매대조" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1469,28 +1469,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>주문 목록 대조</t>
+          <t>구매 내역 대조</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 주문분과 BOM 을 맞춰 본 것입니다.</t>
+          <t>쿠팡 거래명세표 2건 (2026-08-11) · 주식회사 컬리버 · 합계 185,650원 · 함체 5대분 기준</t>
         </is>
       </c>
     </row>
@@ -1502,1065 +1503,1490 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>주문 품목</t>
+          <t>품목</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>BOM 대응</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>확인할 것 / 비고</t>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>확인할 것 / 조치</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>직결나사 접시머리 직결피스 10종 500g</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>10,900</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>(고정용 나사)</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>알루미늄 백플레이트 2t 에는 직결나사가 잘 안 물립니다. 하이박스 기본 내부판이 플라스틱이면 사용 가능. 금속판이면 M4 볼트+너트나 탭 가공 권장</t>
-        </is>
-      </c>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>명세표 ① 70,950원 (배송 3,000 · 할인 1,800 포함)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>몬스툴 전기 인두기 + 받침대 + 땜납 LX1190-30</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>9,710</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>(공구)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>고정식 단자대 30A 8P 터미널블럭 × 5</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2,990</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>33. 단자대 8P</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>적합</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>정격 30A 로 충분. 극 사이 절연 격벽이 있는지 확인 — 220V 와 저압이 한 단자대에 섞입니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>수축 튜브 세트 530p</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>3,590</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>(부속)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>적합</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>압착부 절연·표시용</t>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>5색 DIY 전선 30/26/22/20/18/16AWG UL1007 — 옵션 30AWG/50M</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>14,900</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>38. 배선재</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>★ 사용 불가</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>30AWG = 0.05㎟. 필요한 것은 AWG 16·18·20. 재주문 필요 — 아래 AWG 표 참조</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>원스탑 만능 터미널압착기</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>(공구)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>절연 압착단자용 다이 유무 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>원스탑 만능 터미널압착기</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>(공구)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>고정식 단자대 30A 8P 터미널블럭</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>14,950</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>33. 단자대 8P</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>적합</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>절연 압착단자용 다이가 있는지 확인. 극당 3가닥을 압착단자로 정리해야 합니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>5대분 확보. 극 사이 절연 격벽 유무 확인 — 220V 와 저압이 한 단자대에 섞임</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>어반카 와이오 압착 단자 터미널 320p 세트</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>6,900</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>(부속)</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>확인</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>단자대 나사 규격(M3.5 또는 M4)에 맞는 링/Y 단자가 세트에 있는지 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>단자대 나사 규격(M3.5/M4)에 맞는 링·Y 단자 유무 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>몬스툴 전기 인두기 + 받침대 + 땜납</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>9,710</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>(공구)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>수축 튜브 세트 530p</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3,590</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>(부속)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>적합</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>TVS 소자와 변환기 단자에 필요. 대부분은 나사 단자라 사용처는 적습니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="G11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>5색 DIY 전선 30/26/22/20/18/16AWG UL1007 (옵션 30AWG/50M)</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>14,900</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>38. 배선재</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>★ 확인 필요</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>선택 옵션이 30AWG(0.05㎟) 라면 이 장비에 쓸 수 있는 굵기가 하나도 없습니다. 아래 표 참조</t>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>직결나사 접시머리 직결피스 10종 500g</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>12,700</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>(고정용)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>하이박스 내부판이 철판이면 직결나사 부적합 — M4 볼트+너트 또는 탭 가공</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>주문 합계</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>55990</v>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>원</t>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>명세표 ② 114,700원 (배송 6,000 포함)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>써큘러 커넥터 항공단자 암수세트 4P</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>22,800</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>13. 센서 커넥터</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>★ 수량 부족</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>5대 × 센서 3 = 15세트 필요. 12세트 보유 → 3세트 부족</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>디에스이 HiPPO 노출2구 화이트 콘센트 (나사타입)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>7,750</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>2. 콘센트</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>설계 변경</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>당초 1구 원형 → 노출 2구로 변경됨. 외형이 커져 백플레이트 배치 재확정 필요. 접지극 유무 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>태성전기 하이박스 300×300×165</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>17. 함체</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>적합 · 확정</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>권장 규격과 일치. 내부 유효치수·커버 체결 방식·내부판 재질 실측 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>써큘러 커넥터 항공단자 암수세트 2P</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>3,150</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>11. AC 인입 커넥터</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>★ 극수 부족</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>2P = L·N 뿐. PE(접지) 극이 없음 — 아래 ★ 항목 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>합계 (배송·할인 포함)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>185,650</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>★ 조치가 필요한 것 — 순서대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>문제</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>왜 문제인가</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>조치</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>AC 인입 커넥터에 접지극이 없음 (2P)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>PE 를 받을 극이 없어 접지 계통 전체가 성립하지 않음. SPD 가 서지를 PE 로 뺄 수 없고, 금속 내부판을 본딩할 수 없으며, 콘센트 접지극도 무의미해짐</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>3P 이상 커넥터로 교체 권장. 산 2P 5개는 12V 보조 인출 등 다른 용도로 전용</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>전선 30AWG (0.05㎟)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>전류·강도 모두 부족해 어느 회로에도 쓸 수 없음</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>AWG 16·18·20 재주문</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>AC 와 센서 커넥터가 같은 계열</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>직경이 같으면 AC 220V 플러그가 센서 포트에 물릴 수 있음. 이 설계가 기구적으로 막으려던 사고</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>AC 는 다른 직경(예: 20mm)으로, 센서는 16mm 로 분리. 이미 샀다면 직경 확인 후 라벨·색 병행</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>센서 커넥터 3세트 부족</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>5대 × 3센서 = 15 필요, 12 보유</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>3세트 추가 주문</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>콘센트가 1구 원형 → 노출 2구로 변경</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>외형이 커져 백플레이트 배치와 SH-03 구멍 위치가 바뀜</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>노출 2구 외형·나사 피치 실측 후 PARAMS 갱신 → 도면 재생성</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+      <c r="G28" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>AWG ↔ ㎟ 대조 — 이 장비에 필요한 굵기</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>AWG</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>단면적 ㎟</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>쓰는 곳</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>필요 여부</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>PE 주간선 (사양 1.5㎟ 에 근접)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>필요</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr"/>
-      <c r="F18" s="19" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr"/>
+      <c r="F34" s="19" t="inlineStr"/>
+      <c r="G34" s="19" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>AC L·N / +12V / 0V / 본딩</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>필요</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr"/>
-      <c r="F19" s="19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr"/>
+      <c r="F35" s="19" t="inlineStr"/>
+      <c r="G35" s="19" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>RS485 A·B</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>필요</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr"/>
-      <c r="F20" s="19" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr"/>
+      <c r="F36" s="19" t="inlineStr"/>
+      <c r="G36" s="19" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>불필요</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>쓸 수 없음</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr"/>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr"/>
+      <c r="F39" s="23" t="inlineStr"/>
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>전류·강도 모두 부족</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>★ 필요한 것은 AWG 16 · 18 · 20 세 가지입니다. 주문 옵션이 30AWG 단품이면 16/18/20AWG 를 다시 주문하셔야 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>UL1007 은 PVC 300V 정격, 실리콘 와이어는 보통 UL3132/3239 로 내열 200℃ 입니다. 상품명에 둘이 섞여 있으니 실제 어느 쪽인지 확인하십시오. AC 220V 배선에는 300V 이상 정격이 필요하고, SMPS 근처라면 실리콘 쪽이 내열에 유리합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>RS485 는 함체 안 짧은 구간(변환기→TVS→단자대)이라 낱개 선으로도 되지만 A/B 를 꼬아 주십시오. 센서로 나가는 케이블은 반드시 실드 트위스트 페어여야 하며, 그것은 센서 케이블로 따로 준비합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>아직 주문되지 않은 품목</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>아직 구매되지 않은 품목 (5대분 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>품목</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>SMPS 12V 60W (5A)</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>지정 제품 — 외형·나사 피치 확인</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="9" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>콘센트 1구 원형 220V</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>지정 제품</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>전원</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>파이 전원 어댑터 5.1V 3A</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>공식 어댑터</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>함체</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>하이박스 300×300×165</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>커버 체결 방식 확인 필수</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>함체</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>알루미늄 백플레이트</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>금속. 방열 경로</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>제어</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>라즈베리파이 4 + 7" 디스플레이</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>각 1</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="9" t="inlineStr"/>
-      <c r="F40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>제어</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>USB-RS485 변환기 / SSD / RTC</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>각 1</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr"/>
-      <c r="F41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>커넥터</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>AC 인입 커넥터 + 케이블 플러그</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>각 1</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>센서용과 결합 불가한 형식</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>커넥터</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>M12 A-coded 센서 커넥터</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>3 + 예비 1</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>커넥터</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>M12 현장조립 플러그</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>고어 통기 벤트 M12×1.5</t>
+          <t>SMPS 12V 60W (5A)</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>결로 방지 — 빠뜨리기 쉬움</t>
+          <t>지정 제품 — 외형·나사 피치 확인</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr"/>
       <c r="F45" s="9" t="inlineStr"/>
+      <c r="G45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>방수캡</t>
+          <t>파이 전원 어댑터 5.1V 3A</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>공식 어댑터</t>
+        </is>
+      </c>
       <c r="E46" s="9" t="inlineStr"/>
       <c r="F46" s="9" t="inlineStr"/>
+      <c r="G46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>제어</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>퓨즈홀더 + 퓨즈 (AC 2A / 12V 1A)</t>
+          <t>라즈베리파이 4</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>각 1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr"/>
       <c r="E47" s="9" t="inlineStr"/>
       <c r="F47" s="9" t="inlineStr"/>
+      <c r="G47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>제어</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>SPD 275V (온도퓨즈 내장형)</t>
+          <t>7인치 터치 디스플레이</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>맨 바리스터 금지</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr"/>
       <c r="E48" s="9" t="inlineStr"/>
       <c r="F48" s="9" t="inlineStr"/>
+      <c r="G48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>제어</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>TVS — SM712 / 16V급</t>
+          <t>USB-RS485 변환기</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>각 1</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>GND 단자가 있는 제품</t>
+        </is>
+      </c>
       <c r="E49" s="9" t="inlineStr"/>
       <c r="F49" s="9" t="inlineStr"/>
+      <c r="G49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>제어</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>압착 프레임 (SH-04)</t>
+          <t>USB SSD 또는 산업용 microSD</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>알루미늄 3t 레이저 절단</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr"/>
       <c r="E50" s="9" t="inlineStr"/>
       <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>제어</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>개스킷 테이프 폭5×두께2 / 실리콘 패드 3t</t>
+          <t>RTC DS3231 + CR2032</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>각 1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr"/>
       <c r="E51" s="9" t="inlineStr"/>
       <c r="F51" s="9" t="inlineStr"/>
+      <c r="G51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>제어</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>M3 스탠드오프 Ø8 접착식</t>
+          <t>파이 방열 케이스</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>길이는 시제품 실측 후</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr"/>
       <c r="E52" s="9" t="inlineStr"/>
       <c r="F52" s="9" t="inlineStr"/>
+      <c r="G52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>SUS316 M4 핀-인-톡스 볼트 + 전용 비트</t>
+          <t>AC 인입 커넥터 3P 이상</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>6 / 1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>탬퍼 방지</t>
+          <t>★ 접지극 필수</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr"/>
       <c r="F53" s="9" t="inlineStr"/>
+      <c r="G53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>봉인 라벨 VOID</t>
+          <t>센서 커넥터 4P 추가</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>12 보유 → 15 필요</t>
+        </is>
+      </c>
       <c r="E54" s="9" t="inlineStr"/>
       <c r="F54" s="9" t="inlineStr"/>
+      <c r="G54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>접지 스터드 M4 + 톱니와셔</t>
+          <t>고어 통기 벤트 M12×1.5</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>★ 결로 방지 — 빠뜨리기 쉬움</t>
+        </is>
+      </c>
       <c r="E55" s="9" t="inlineStr"/>
       <c r="F55" s="9" t="inlineStr"/>
+      <c r="G55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>실리카겔 50g / 열전도 패드</t>
+          <t>방수캡</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>각 1</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>미사용 포트용</t>
+        </is>
+      </c>
       <c r="E56" s="9" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr"/>
+      <c r="G56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>배선</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>종단저항 120Ω</t>
+          <t>퓨즈홀더 + 퓨즈 (AC 2A / 12V 1A)</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>케이블 10m 초과 시</t>
-        </is>
-      </c>
+          <t>각 5</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr"/>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
+      <c r="G57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>배선</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>케이블 타이 앵커 (접착식)</t>
+          <t>SPD 275V 온도퓨즈 내장형</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>1식</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>맨 바리스터 금지</t>
+        </is>
+      </c>
       <c r="E58" s="9" t="inlineStr"/>
       <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>배선</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>RS485용 실드 트위스트 페어 센서 케이블</t>
+          <t>TVS — SM712 / 16V급</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>현장별</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>0.5㎟ 이상. 50m 초과면 0.75㎟</t>
-        </is>
-      </c>
+          <t>각 5</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr"/>
       <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
+      <c r="G59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>라벨</t>
+          <t>기구</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>정격·경고·커넥터·시리얼 라벨</t>
+          <t>압착 프레임 (SH-04) 알루미늄 3t</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>1식</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>전면: 환경 모니터링 시스템 / 주식회사 컬리버</t>
+          <t>레이저 절단 발주</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr"/>
       <c r="F60" s="9" t="inlineStr"/>
+      <c r="G60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>개스킷 테이프 폭5×두께2</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>1롤</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>실리콘 패드 3t</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="9" t="inlineStr"/>
+      <c r="G62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>M3 스탠드오프 Ø8 접착식</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>길이는 시제품 실측 후</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr"/>
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>SUS316 M4 핀-인-톡스 볼트</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>탬퍼 방지</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr"/>
+      <c r="F64" s="9" t="inlineStr"/>
+      <c r="G64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>전용 톡스 비트</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>A/S 키트에만</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>봉인 라벨 VOID</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr"/>
+      <c r="E66" s="9" t="inlineStr"/>
+      <c r="F66" s="9" t="inlineStr"/>
+      <c r="G66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>접지 스터드 M4 + 톱니와셔</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>★ AC 3P 커넥터 확보 후</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr"/>
+      <c r="F67" s="9" t="inlineStr"/>
+      <c r="G67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>실리카겔 50g</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr"/>
+      <c r="E68" s="9" t="inlineStr"/>
+      <c r="F68" s="9" t="inlineStr"/>
+      <c r="G68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>기구</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>열전도 패드</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr"/>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>전선 AWG 16 / 18 / 20</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>각 1롤</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>★ 재주문</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr"/>
+      <c r="F70" s="9" t="inlineStr"/>
+      <c r="G70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>RS485 실드 트위스트 페어 센서 케이블</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>현장별</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>0.5㎟ 이상</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>종단저항 120Ω</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>케이블 10m 초과 시</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr"/>
+      <c r="F72" s="9" t="inlineStr"/>
+      <c r="G72" s="9" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>배선</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>케이블 타이 앵커</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>1식</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>라벨</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>정격·경고·커넥터·시리얼 라벨</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>5식</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>전면: 환경 모니터링 시스템 / 주식회사 컬리버</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr"/>
+      <c r="F74" s="9" t="inlineStr"/>
+      <c r="G74" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/raspberry-pi/enclosure/xlsx/hardware.xlsx
+++ b/raspberry-pi/enclosure/xlsx/hardware.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>커넥터 예비 1개는 방수캡</t>
+          <t>하면 원형 타공 4개소 전부 사용</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>12 보유 → 15 필요</t>
+          <t>12 보유 → 15 필요 (5대 × 3)</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr"/>
@@ -2528,17 +2528,17 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>고어 통기 벤트 M12×1.5</t>
+          <t>방수캡</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>★ 결로 방지 — 빠뜨리기 쉬움</t>
+          <t>현장 예비</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr"/>
@@ -2548,24 +2548,20 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>방수캡</t>
+          <t>퓨즈홀더 + 퓨즈 (AC 2A / 12V 1A)</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>미사용 포트용</t>
-        </is>
-      </c>
+          <t>각 5</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr"/>
       <c r="E56" s="9" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr"/>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2578,15 +2574,19 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>퓨즈홀더 + 퓨즈 (AC 2A / 12V 1A)</t>
+          <t>SPD 275V 온도퓨즈 내장형</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>각 5</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>맨 바리스터 금지</t>
+        </is>
+      </c>
       <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
@@ -2599,19 +2599,15 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>SPD 275V 온도퓨즈 내장형</t>
+          <t>TVS — SM712 / 16V급</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>맨 바리스터 금지</t>
-        </is>
-      </c>
+          <t>각 5</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr"/>
       <c r="E58" s="9" t="inlineStr"/>
       <c r="F58" s="9" t="inlineStr"/>
       <c r="G58" s="9" t="inlineStr"/>
@@ -2619,20 +2615,24 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>기구</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>TVS — SM712 / 16V급</t>
+          <t>압착 프레임 (SH-04) 알루미늄 3t</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>각 5</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>레이저 절단 발주</t>
+        </is>
+      </c>
       <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
@@ -2645,19 +2645,15 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>압착 프레임 (SH-04) 알루미늄 3t</t>
+          <t>개스킷 테이프 폭5×두께2</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>레이저 절단 발주</t>
-        </is>
-      </c>
+          <t>1롤</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr"/>
       <c r="E60" s="9" t="inlineStr"/>
       <c r="F60" s="9" t="inlineStr"/>
       <c r="G60" s="9" t="inlineStr"/>
@@ -2670,12 +2666,12 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>개스킷 테이프 폭5×두께2</t>
+          <t>실리콘 패드 3t</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>1롤</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr"/>
@@ -2691,15 +2687,19 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>실리콘 패드 3t</t>
+          <t>M3 스탠드오프 Ø8 접착식</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>길이는 시제품 실측 후</t>
+        </is>
+      </c>
       <c r="E62" s="9" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr"/>
       <c r="G62" s="9" t="inlineStr"/>
@@ -2712,17 +2712,17 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>M3 스탠드오프 Ø8 접착식</t>
+          <t>SUS316 M4 핀-인-톡스 볼트</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>길이는 시제품 실측 후</t>
+          <t>탬퍼 방지</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr"/>
@@ -2737,17 +2737,17 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>SUS316 M4 핀-인-톡스 볼트</t>
+          <t>전용 톡스 비트</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>탬퍼 방지</t>
+          <t>A/S 키트에만</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr"/>
@@ -2762,19 +2762,15 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>전용 톡스 비트</t>
+          <t>봉인 라벨 VOID</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>A/S 키트에만</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr"/>
       <c r="G65" s="9" t="inlineStr"/>
@@ -2787,15 +2783,19 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>봉인 라벨 VOID</t>
+          <t>접지 스터드 M4 + 톱니와셔</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>★ AC 3P 커넥터 확보 후</t>
+        </is>
+      </c>
       <c r="E66" s="9" t="inlineStr"/>
       <c r="F66" s="9" t="inlineStr"/>
       <c r="G66" s="9" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>접지 스터드 M4 + 톱니와셔</t>
+          <t>실리카겔 50g</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -2816,11 +2816,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>★ AC 3P 커넥터 확보 후</t>
-        </is>
-      </c>
+      <c r="D67" s="9" t="inlineStr"/>
       <c r="E67" s="9" t="inlineStr"/>
       <c r="F67" s="9" t="inlineStr"/>
       <c r="G67" s="9" t="inlineStr"/>
@@ -2833,7 +2829,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>실리카겔 50g</t>
+          <t>열전도 패드</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -2849,20 +2845,24 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>기구</t>
+          <t>배선</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>열전도 패드</t>
+          <t>전선 AWG 16 / 18 / 20</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr"/>
+          <t>각 1롤</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>★ 재주문</t>
+        </is>
+      </c>
       <c r="E69" s="9" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr"/>
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>전선 AWG 16 / 18 / 20</t>
+          <t>RS485 실드 트위스트 페어 센서 케이블</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>각 1롤</t>
+          <t>현장별</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>★ 재주문</t>
+          <t>0.5㎟ 이상</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr"/>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>RS485 실드 트위스트 페어 센서 케이블</t>
+          <t>종단저항 120Ω</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>현장별</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>0.5㎟ 이상</t>
+          <t>케이블 10m 초과 시</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr"/>
@@ -2925,19 +2925,15 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>종단저항 120Ω</t>
+          <t>케이블 타이 앵커</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>케이블 10m 초과 시</t>
-        </is>
-      </c>
+          <t>1식</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr"/>
       <c r="E72" s="9" t="inlineStr"/>
       <c r="F72" s="9" t="inlineStr"/>
       <c r="G72" s="9" t="inlineStr"/>
@@ -2945,48 +2941,27 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>배선</t>
+          <t>라벨</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>케이블 타이 앵커</t>
+          <t>정격·경고·커넥터·시리얼 라벨</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>1식</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr"/>
+          <t>5식</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>전면: 환경 모니터링 시스템 / 주식회사 컬리버</t>
+        </is>
+      </c>
       <c r="E73" s="9" t="inlineStr"/>
       <c r="F73" s="9" t="inlineStr"/>
       <c r="G73" s="9" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>라벨</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>정격·경고·커넥터·시리얼 라벨</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>5식</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>전면: 환경 모니터링 시스템 / 주식회사 컬리버</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr"/>
-      <c r="F74" s="9" t="inlineStr"/>
-      <c r="G74" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3474,7 +3449,7 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
@@ -3483,7 +3458,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>3 사용 + 예비 1</t>
+          <t>예비 포트 없음</t>
         </is>
       </c>
     </row>
@@ -3531,25 +3506,25 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>통기 벤트</t>
+          <t>(삭제) 통기 벤트</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>GORE Screw-In Series M12×1.5</t>
+          <t>하면 타공 4개소 한정 결정으로 제외</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>확인완료</t>
+          <t>결정됨</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>결로 방지 필수</t>
+          <t>결로 대책은 실리카겔뿐</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3557,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>예비 포트용</t>
+          <t>현장 예비</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4308,7 @@
       </c>
       <c r="E45" s="11">
         <f>COUNTIF(F5:F43,"확인완료")</f>
-        <v>3</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -4344,7 +4319,7 @@
       </c>
       <c r="E46" s="11">
         <f>COUNTIF(F5:F43,"확인필요")</f>
-        <v>34</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -4355,7 +4330,7 @@
       </c>
       <c r="E47" s="11">
         <f>COUNTIF(F5:F43,"제작")</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6085,7 +6060,7 @@
       </c>
       <c r="B11" s="17">
         <f>SUM(B5:B10)</f>
-        <v>14.6</v>
+        <v/>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
@@ -6107,7 +6082,7 @@
       </c>
       <c r="B12" s="12">
         <f>SUMIF(D5:D10,"Y",B5:B10)</f>
-        <v>13.4</v>
+        <v/>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -6243,7 +6218,7 @@
       </c>
       <c r="B21" s="8">
         <f>2*(B17*B18+B17*B19+B18*B19)/1000000</f>
-        <v>0.378</v>
+        <v/>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -6265,7 +6240,7 @@
       </c>
       <c r="B22" s="8">
         <f>B21-(B17*B18)/1000000</f>
-        <v>0.288</v>
+        <v/>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -6287,7 +6262,7 @@
       </c>
       <c r="B23" s="8">
         <f>B12/(B20*B22)</f>
-        <v>13.29</v>
+        <v/>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -6309,7 +6284,7 @@
       </c>
       <c r="B24" s="17">
         <f>40+B23</f>
-        <v>53.29</v>
+        <v/>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -6449,31 +6424,31 @@
       </c>
       <c r="E5" s="8">
         <f>B5-$B$17</f>
-        <v>85</v>
+        <v/>
       </c>
       <c r="F5" s="8">
         <f>C5-$B$17</f>
-        <v>135</v>
+        <v/>
       </c>
       <c r="G5" s="8">
         <f>D5-$B$18</f>
-        <v>57</v>
+        <v/>
       </c>
       <c r="H5" s="8">
         <f>E5-$B$19</f>
-        <v>-165</v>
+        <v/>
       </c>
       <c r="I5" s="8">
         <f>F5-$B$20</f>
-        <v>-85</v>
+        <v/>
       </c>
       <c r="J5" s="8">
         <f>G5-$B$21</f>
-        <v>-63</v>
-      </c>
-      <c r="K5" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="8">
         <f>IF(AND(H5&gt;=0,I5&gt;=0,J5&gt;=0),"가능","불가")</f>
-        <v>불가</v>
+        <v/>
       </c>
       <c r="L5" s="8" t="inlineStr"/>
     </row>
@@ -6492,31 +6467,31 @@
       </c>
       <c r="E6" s="8">
         <f>B6-$B$17</f>
-        <v>135</v>
+        <v/>
       </c>
       <c r="F6" s="8">
         <f>C6-$B$17</f>
-        <v>135</v>
+        <v/>
       </c>
       <c r="G6" s="8">
         <f>D6-$B$18</f>
-        <v>67</v>
+        <v/>
       </c>
       <c r="H6" s="8">
         <f>E6-$B$19</f>
-        <v>-115</v>
+        <v/>
       </c>
       <c r="I6" s="8">
         <f>F6-$B$20</f>
-        <v>-85</v>
+        <v/>
       </c>
       <c r="J6" s="8">
         <f>G6-$B$21</f>
-        <v>-53</v>
-      </c>
-      <c r="K6" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="8">
         <f>IF(AND(H6&gt;=0,I6&gt;=0,J6&gt;=0),"가능","불가")</f>
-        <v>불가</v>
+        <v/>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
     </row>
@@ -6535,31 +6510,31 @@
       </c>
       <c r="E7" s="8">
         <f>B7-$B$17</f>
-        <v>135</v>
+        <v/>
       </c>
       <c r="F7" s="8">
         <f>C7-$B$17</f>
-        <v>185</v>
+        <v/>
       </c>
       <c r="G7" s="8">
         <f>D7-$B$18</f>
-        <v>107</v>
+        <v/>
       </c>
       <c r="H7" s="8">
         <f>E7-$B$19</f>
-        <v>-115</v>
+        <v/>
       </c>
       <c r="I7" s="8">
         <f>F7-$B$20</f>
-        <v>-35</v>
+        <v/>
       </c>
       <c r="J7" s="8">
         <f>G7-$B$21</f>
-        <v>-13</v>
-      </c>
-      <c r="K7" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K7" s="8">
         <f>IF(AND(H7&gt;=0,I7&gt;=0,J7&gt;=0),"가능","불가")</f>
-        <v>불가</v>
+        <v/>
       </c>
       <c r="L7" s="8" t="inlineStr"/>
     </row>
@@ -6578,31 +6553,31 @@
       </c>
       <c r="E8" s="8">
         <f>B8-$B$17</f>
-        <v>185</v>
+        <v/>
       </c>
       <c r="F8" s="8">
         <f>C8-$B$17</f>
-        <v>285</v>
+        <v/>
       </c>
       <c r="G8" s="8">
         <f>D8-$B$18</f>
-        <v>107</v>
+        <v/>
       </c>
       <c r="H8" s="8">
         <f>E8-$B$19</f>
-        <v>-65</v>
+        <v/>
       </c>
       <c r="I8" s="8">
         <f>F8-$B$20</f>
-        <v>65</v>
+        <v/>
       </c>
       <c r="J8" s="8">
         <f>G8-$B$21</f>
-        <v>-13</v>
-      </c>
-      <c r="K8" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="8">
         <f>IF(AND(H8&gt;=0,I8&gt;=0,J8&gt;=0),"가능","불가")</f>
-        <v>불가</v>
+        <v/>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -6625,31 +6600,31 @@
       </c>
       <c r="E9" s="19">
         <f>B9-$B$17</f>
-        <v>285</v>
+        <v/>
       </c>
       <c r="F9" s="19">
         <f>C9-$B$17</f>
-        <v>285</v>
+        <v/>
       </c>
       <c r="G9" s="19">
         <f>D9-$B$18</f>
-        <v>142</v>
+        <v/>
       </c>
       <c r="H9" s="19">
         <f>E9-$B$19</f>
-        <v>35</v>
+        <v/>
       </c>
       <c r="I9" s="19">
         <f>F9-$B$20</f>
-        <v>65</v>
+        <v/>
       </c>
       <c r="J9" s="19">
         <f>G9-$B$21</f>
-        <v>22</v>
-      </c>
-      <c r="K9" s="19" t="str">
+        <v/>
+      </c>
+      <c r="K9" s="19">
         <f>IF(AND(H9&gt;=0,I9&gt;=0,J9&gt;=0),"가능","불가")</f>
-        <v>가능</v>
+        <v/>
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
@@ -6672,31 +6647,31 @@
       </c>
       <c r="E10" s="8">
         <f>B10-$B$17</f>
-        <v>285</v>
+        <v/>
       </c>
       <c r="F10" s="8">
         <f>C10-$B$17</f>
-        <v>385</v>
+        <v/>
       </c>
       <c r="G10" s="8">
         <f>D10-$B$18</f>
-        <v>127</v>
+        <v/>
       </c>
       <c r="H10" s="8">
         <f>E10-$B$19</f>
-        <v>35</v>
+        <v/>
       </c>
       <c r="I10" s="8">
         <f>F10-$B$20</f>
-        <v>165</v>
+        <v/>
       </c>
       <c r="J10" s="8">
         <f>G10-$B$21</f>
-        <v>7</v>
-      </c>
-      <c r="K10" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K10" s="8">
         <f>IF(AND(H10&gt;=0,I10&gt;=0,J10&gt;=0),"가능","불가")</f>
-        <v>가능</v>
+        <v/>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -6719,31 +6694,31 @@
       </c>
       <c r="E11" s="8">
         <f>B11-$B$17</f>
-        <v>385</v>
+        <v/>
       </c>
       <c r="F11" s="8">
         <f>C11-$B$17</f>
-        <v>485</v>
+        <v/>
       </c>
       <c r="G11" s="8">
         <f>D11-$B$18</f>
-        <v>137</v>
+        <v/>
       </c>
       <c r="H11" s="8">
         <f>E11-$B$19</f>
-        <v>135</v>
+        <v/>
       </c>
       <c r="I11" s="8">
         <f>F11-$B$20</f>
-        <v>265</v>
+        <v/>
       </c>
       <c r="J11" s="8">
         <f>G11-$B$21</f>
-        <v>17</v>
-      </c>
-      <c r="K11" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K11" s="8">
         <f>IF(AND(H11&gt;=0,I11&gt;=0,J11&gt;=0),"가능","불가")</f>
-        <v>가능</v>
+        <v/>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -6766,31 +6741,31 @@
       </c>
       <c r="E12" s="8">
         <f>B12-$B$17</f>
-        <v>485</v>
+        <v/>
       </c>
       <c r="F12" s="8">
         <f>C12-$B$17</f>
-        <v>585</v>
+        <v/>
       </c>
       <c r="G12" s="8">
         <f>D12-$B$18</f>
-        <v>167</v>
+        <v/>
       </c>
       <c r="H12" s="8">
         <f>E12-$B$19</f>
-        <v>235</v>
+        <v/>
       </c>
       <c r="I12" s="8">
         <f>F12-$B$20</f>
-        <v>365</v>
+        <v/>
       </c>
       <c r="J12" s="8">
         <f>G12-$B$21</f>
-        <v>47</v>
-      </c>
-      <c r="K12" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K12" s="8">
         <f>IF(AND(H12&gt;=0,I12&gt;=0,J12&gt;=0),"가능","불가")</f>
-        <v>가능</v>
+        <v/>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -6813,31 +6788,31 @@
       </c>
       <c r="E13" s="8">
         <f>B13-$B$17</f>
-        <v>585</v>
+        <v/>
       </c>
       <c r="F13" s="8">
         <f>C13-$B$17</f>
-        <v>685</v>
+        <v/>
       </c>
       <c r="G13" s="8">
         <f>D13-$B$18</f>
-        <v>177</v>
+        <v/>
       </c>
       <c r="H13" s="8">
         <f>E13-$B$19</f>
-        <v>335</v>
+        <v/>
       </c>
       <c r="I13" s="8">
         <f>F13-$B$20</f>
-        <v>465</v>
+        <v/>
       </c>
       <c r="J13" s="8">
         <f>G13-$B$21</f>
-        <v>57</v>
-      </c>
-      <c r="K13" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K13" s="8">
         <f>IF(AND(H13&gt;=0,I13&gt;=0,J13&gt;=0),"가능","불가")</f>
-        <v>가능</v>
+        <v/>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -6860,31 +6835,31 @@
       </c>
       <c r="E14" s="8">
         <f>B14-$B$17</f>
-        <v>75</v>
+        <v/>
       </c>
       <c r="F14" s="8">
         <f>C14-$B$17</f>
-        <v>120</v>
+        <v/>
       </c>
       <c r="G14" s="8">
         <f>D14-$B$18</f>
-        <v>62</v>
+        <v/>
       </c>
       <c r="H14" s="8">
         <f>E14-$B$19</f>
-        <v>-175</v>
+        <v/>
       </c>
       <c r="I14" s="8">
         <f>F14-$B$20</f>
-        <v>-100</v>
+        <v/>
       </c>
       <c r="J14" s="8">
         <f>G14-$B$21</f>
-        <v>-58</v>
-      </c>
-      <c r="K14" s="8" t="str">
+        <v/>
+      </c>
+      <c r="K14" s="8">
         <f>IF(AND(H14&gt;=0,I14&gt;=0,J14&gt;=0),"가능","불가")</f>
-        <v>불가</v>
+        <v/>
       </c>
       <c r="L14" s="8" t="inlineStr"/>
     </row>
@@ -6988,7 +6963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7053,21 +7028,21 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>VENT</t>
+          <t>센서 1 pH</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>고어텍스 통기 벤트 M12×1.5</t>
+          <t>M12 A-coded</t>
         </is>
       </c>
     </row>
@@ -7079,11 +7054,11 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>센서 1 pH</t>
+          <t>센서 2 DO</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-54</v>
+        <v>-66</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>100</v>
@@ -7105,11 +7080,11 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>센서 2 DO</t>
+          <t>센서 3 EC</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-18</v>
+        <v>-30</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>100</v>
@@ -7131,11 +7106,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>센서 3 EC</t>
+          <t>AC 인입</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>100</v>
@@ -7145,126 +7120,118 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>M12 A-coded</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SH-02 하부면</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>예비</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>방수캡, 미결선</t>
+          <t>센서용과 결합 불가한 형식</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SH-02 하부면</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>AC 인입</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>센서용과 결합 불가한 형식</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>※ Ø16.5 는 M16×1.5 전면체결형 기준입니다. 후면체결형은 Ø12.5 로 다릅니다 — 커넥터 데이터시트 확인 필수</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>※ Ø16.5 는 M16×1.5 전면체결형 기준입니다. 후면체결형은 Ø12.5 로 다릅니다 — 커넥터 데이터시트 확인 필수</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>도면</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>지름 Ø</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>SH-03 백플레이트</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>SMPS-1</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>-115</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>⚠ 나사 피치 추정 110 × 78</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>도면</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>지름 Ø</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SH-03 백플레이트</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>SMPS-2</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SH-03 백플레이트</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>SMPS-1</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SMPS-3</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>-115</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>⚠ 나사 피치 추정 110 × 78</t>
-        </is>
-      </c>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7274,14 +7241,14 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SMPS-2</t>
+          <t>SMPS-4</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>4.5</v>
@@ -7289,26 +7256,30 @@
       <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>SH-03 백플레이트</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SMPS-3</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-115</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>콘센트-1</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>⚠ 상하 2점 추정 피치 60</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7318,14 +7289,14 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SMPS-4</t>
+          <t>콘센트-2</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>4.5</v>
@@ -7340,21 +7311,21 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>콘센트-1</t>
+          <t>단자대-1</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>68</v>
+        <v>-96</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>28</v>
+        <v>-78</v>
       </c>
       <c r="E19" s="9" t="n">
         <v>4.5</v>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>⚠ 상하 2점 추정 피치 60</t>
+          <t>⚠ 피치 추정 92</t>
         </is>
       </c>
     </row>
@@ -7366,14 +7337,14 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>콘센트-2</t>
+          <t>단자대-2</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>68</v>
+        <v>-4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>88</v>
+        <v>-78</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>4.5</v>
@@ -7381,81 +7352,33 @@
       <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>SH-03 백플레이트</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>단자대-1</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>-96</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>-78</v>
-      </c>
-      <c r="E21" s="9" t="n">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>접지 스터드</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-112</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>⚠ 피치 추정 92</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>SH-03 백플레이트</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>단자대-2</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-78</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>톱니와셔로 산화막 관통</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>SH-03 백플레이트</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>접지 스터드</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>-112</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>톱니와셔로 산화막 관통</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>※ SMPS·콘센트·단자대 세 부품의 외형과 나사 피치는 실물 확인 전 추정치입니다. 실측 후 확정하십시오.</t>
         </is>
@@ -8053,7 +7976,7 @@
       </c>
       <c r="B22" s="8">
         <f>B20*B21*2/B19</f>
-        <v>3.56</v>
+        <v/>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -8074,7 +7997,7 @@
       </c>
       <c r="B23" s="8">
         <f>B18*B22</f>
-        <v>0.3204</v>
+        <v/>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -8095,7 +8018,7 @@
       </c>
       <c r="B24" s="8">
         <f>12-B23</f>
-        <v>11.6796</v>
+        <v/>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -8116,7 +8039,7 @@
       </c>
       <c r="B25" s="17">
         <f>B24-9</f>
-        <v>2.6796</v>
+        <v/>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
